--- a/3_PPTurnover/input/dict/Dict_EnergyEfficiency.xlsx
+++ b/3_PPTurnover/input/dict/Dict_EnergyEfficiency.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model-main\3_PPTurnover\input\dict\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\92978\Desktop\Unit-level-Turnover-Model\3_PPTurnover\input\dict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A6CABA-7953-4B33-B81B-51B9784819A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1673BEFE-1113-443E-B825-745D78E60DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11438" yWindow="0" windowWidth="11684" windowHeight="13763" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coal" sheetId="1" r:id="rId1"/>
+    <sheet name="Readme" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Unit</t>
   </si>
@@ -46,30 +47,28 @@
   </si>
   <si>
     <t>kt/kWh</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Coal</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This file provides energy consumption intensities for newly built plants, estimated from the regional 25th-percentile values of existing units.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -101,15 +100,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -120,27 +118,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -164,21 +147,19 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -484,208 +465,224 @@
   <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="9.06640625" style="2"/>
-    <col min="4" max="4" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="1"/>
+    <col min="4" max="32" width="13.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="13.9" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D1" s="2">
         <v>2022</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E1" s="2">
         <v>2023</v>
       </c>
-      <c r="F1" s="1">
+      <c r="F1" s="2">
         <v>2024</v>
       </c>
-      <c r="G1" s="1">
+      <c r="G1" s="2">
         <v>2025</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="2">
         <v>2026</v>
       </c>
-      <c r="I1" s="1">
+      <c r="I1" s="2">
         <v>2027</v>
       </c>
-      <c r="J1" s="1">
+      <c r="J1" s="2">
         <v>2028</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="2">
         <v>2029</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="2">
         <v>2030</v>
       </c>
-      <c r="M1" s="1">
+      <c r="M1" s="2">
         <v>2031</v>
       </c>
-      <c r="N1" s="1">
+      <c r="N1" s="2">
         <v>2032</v>
       </c>
-      <c r="O1" s="1">
+      <c r="O1" s="2">
         <v>2033</v>
       </c>
-      <c r="P1" s="1">
+      <c r="P1" s="2">
         <v>2034</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="Q1" s="2">
         <v>2035</v>
       </c>
-      <c r="R1" s="1">
+      <c r="R1" s="2">
         <v>2036</v>
       </c>
-      <c r="S1" s="1">
+      <c r="S1" s="2">
         <v>2037</v>
       </c>
-      <c r="T1" s="1">
+      <c r="T1" s="2">
         <v>2038</v>
       </c>
-      <c r="U1" s="1">
+      <c r="U1" s="2">
         <v>2039</v>
       </c>
-      <c r="V1" s="1">
+      <c r="V1" s="2">
         <v>2040</v>
       </c>
-      <c r="W1" s="1">
+      <c r="W1" s="2">
         <v>2041</v>
       </c>
-      <c r="X1" s="1">
+      <c r="X1" s="2">
         <v>2042</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="Y1" s="2">
         <v>2043</v>
       </c>
-      <c r="Z1" s="1">
+      <c r="Z1" s="2">
         <v>2044</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="AA1" s="2">
         <v>2045</v>
       </c>
-      <c r="AB1" s="1">
+      <c r="AB1" s="2">
         <v>2046</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="AC1" s="2">
         <v>2047</v>
       </c>
-      <c r="AD1" s="1">
+      <c r="AD1" s="2">
         <v>2048</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AE1" s="2">
         <v>2049</v>
       </c>
-      <c r="AF1" s="1">
+      <c r="AF1" s="2">
         <v>2050</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="13.9" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="E2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="F2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="G2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="H2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="I2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="J2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="K2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="L2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="M2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="N2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="O2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="P2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="R2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="S2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="T2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="U2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="V2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="W2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="X2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="Y2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="Z2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="AA2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="AB2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="AC2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="AD2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="AE2" s="7">
-        <v>3.8590596060384598E-7</v>
-      </c>
-      <c r="AF2">
+      <c r="D2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="E2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="F2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="G2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="H2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="I2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="J2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="K2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="L2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="M2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="N2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="O2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="P2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="R2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="S2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="T2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="U2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="V2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="W2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="X2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>3.8590596060384598E-7</v>
+      </c>
+      <c r="AF2" s="7">
         <v>3.8589098101472782E-7</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A25416-2525-4F98-8454-B25C374E14F2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="13.9" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>